--- a/Result/profitability/5403.xlsx
+++ b/Result/profitability/5403.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.91</v>
+        <v>1.94375</v>
       </c>
       <c r="N2" t="n">
-        <v>36.66875</v>
+        <v>36.65125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.73625</v>
+        <v>1.635</v>
       </c>
       <c r="N3" t="n">
-        <v>34.00125</v>
+        <v>34.8025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.41</v>
+        <v>1.43875</v>
       </c>
       <c r="N4" t="n">
-        <v>31.9475</v>
+        <v>32.75625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.205</v>
+        <v>1.22625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.3975</v>
+        <v>29.745</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9762500000000001</v>
+        <v>1.0125</v>
       </c>
       <c r="N6" t="n">
-        <v>26.44</v>
+        <v>26.21625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0.79</v>
+        <v>0.70875</v>
       </c>
       <c r="N7" t="n">
-        <v>23.45375</v>
+        <v>23.84</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.6375</v>
       </c>
       <c r="N8" t="n">
-        <v>22.16</v>
+        <v>22.8425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5403</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>869</v>
+      </c>
+      <c r="D75" t="n">
+        <v>501</v>
+      </c>
+      <c r="E75" t="n">
+        <v>368</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>193</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>205</v>
+      </c>
+      <c r="K75" t="n">
+        <v>162</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.58499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5211267605633805</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.460000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1479273909509617</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1700000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.085427135678392</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.779999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07021975246274303</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
